--- a/data/indecnacional.xlsx
+++ b/data/indecnacional.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q110"/>
+  <dimension ref="A1:Q111"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="14" max="14" width="20.7109375" style="2" customWidth="1"/>
@@ -6443,6 +6443,61 @@
         </is>
       </c>
     </row>
+    <row r="111">
+      <c r="A111">
+        <v>2.9</v>
+      </c>
+      <c r="B111">
+        <v>3.3</v>
+      </c>
+      <c r="C111">
+        <v>0.6</v>
+      </c>
+      <c r="D111">
+        <v>0</v>
+      </c>
+      <c r="E111">
+        <v>6.8</v>
+      </c>
+      <c r="F111">
+        <v>2.6</v>
+      </c>
+      <c r="G111">
+        <v>2.5</v>
+      </c>
+      <c r="H111">
+        <v>2</v>
+      </c>
+      <c r="I111">
+        <v>1.8</v>
+      </c>
+      <c r="J111">
+        <v>2.3</v>
+      </c>
+      <c r="K111">
+        <v>1.2</v>
+      </c>
+      <c r="L111">
+        <v>3</v>
+      </c>
+      <c r="M111">
+        <v>3.3</v>
+      </c>
+      <c r="N111" s="2">
+        <v>46054</v>
+      </c>
+      <c r="O111">
+        <v>2026</v>
+      </c>
+      <c r="P111">
+        <v>2</v>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>Feb</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/indecnacional.xlsx
+++ b/data/indecnacional.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q111"/>
+  <dimension ref="A1:Q112"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="14" max="14" width="20.7109375" style="2" customWidth="1"/>
@@ -6498,6 +6498,61 @@
         </is>
       </c>
     </row>
+    <row r="112">
+      <c r="A112">
+        <v>3.4</v>
+      </c>
+      <c r="B112">
+        <v>3.4</v>
+      </c>
+      <c r="C112">
+        <v>2.1</v>
+      </c>
+      <c r="D112">
+        <v>3.1</v>
+      </c>
+      <c r="E112">
+        <v>3.7</v>
+      </c>
+      <c r="F112">
+        <v>1.3</v>
+      </c>
+      <c r="G112">
+        <v>2.6</v>
+      </c>
+      <c r="H112">
+        <v>4.1</v>
+      </c>
+      <c r="I112">
+        <v>2.9</v>
+      </c>
+      <c r="J112">
+        <v>3.6</v>
+      </c>
+      <c r="K112">
+        <v>12.1</v>
+      </c>
+      <c r="L112">
+        <v>3.4</v>
+      </c>
+      <c r="M112">
+        <v>1.7</v>
+      </c>
+      <c r="N112" s="2">
+        <v>46082</v>
+      </c>
+      <c r="O112">
+        <v>2026</v>
+      </c>
+      <c r="P112">
+        <v>3</v>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/indecnacional.xlsx
+++ b/data/indecnacional.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q112"/>
+  <dimension ref="A1:Q113"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="14" max="14" width="20.7109375" style="2" customWidth="1"/>
@@ -6553,6 +6553,61 @@
         </is>
       </c>
     </row>
+    <row r="113">
+      <c r="A113">
+        <v>2.6</v>
+      </c>
+      <c r="B113">
+        <v>1.5</v>
+      </c>
+      <c r="C113">
+        <v>1.9</v>
+      </c>
+      <c r="D113">
+        <v>3.2</v>
+      </c>
+      <c r="E113">
+        <v>3.5</v>
+      </c>
+      <c r="F113">
+        <v>2.9</v>
+      </c>
+      <c r="G113">
+        <v>2.5</v>
+      </c>
+      <c r="H113">
+        <v>4.4</v>
+      </c>
+      <c r="I113">
+        <v>4.1</v>
+      </c>
+      <c r="J113">
+        <v>1</v>
+      </c>
+      <c r="K113">
+        <v>4.2</v>
+      </c>
+      <c r="L113">
+        <v>2.6</v>
+      </c>
+      <c r="M113">
+        <v>2.4</v>
+      </c>
+      <c r="N113" s="2">
+        <v>46113</v>
+      </c>
+      <c r="O113">
+        <v>2026</v>
+      </c>
+      <c r="P113">
+        <v>4</v>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>Apr</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/indecnacional.xlsx
+++ b/data/indecnacional.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q113"/>
+  <dimension ref="A1:Q114"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="14" max="14" width="20.7109375" style="2" customWidth="1"/>
@@ -6608,6 +6608,61 @@
         </is>
       </c>
     </row>
+    <row r="114">
+      <c r="A114">
+        <v>2.1</v>
+      </c>
+      <c r="B114">
+        <v>2.5</v>
+      </c>
+      <c r="C114">
+        <v>0.8</v>
+      </c>
+      <c r="D114">
+        <v>0.3</v>
+      </c>
+      <c r="E114">
+        <v>2.6</v>
+      </c>
+      <c r="F114">
+        <v>1.4</v>
+      </c>
+      <c r="G114">
+        <v>2.6</v>
+      </c>
+      <c r="H114">
+        <v>2</v>
+      </c>
+      <c r="I114">
+        <v>3.4</v>
+      </c>
+      <c r="J114">
+        <v>2.8</v>
+      </c>
+      <c r="K114">
+        <v>2.9</v>
+      </c>
+      <c r="L114">
+        <v>1.8</v>
+      </c>
+      <c r="M114">
+        <v>2.4</v>
+      </c>
+      <c r="N114" s="2">
+        <v>46143</v>
+      </c>
+      <c r="O114">
+        <v>2026</v>
+      </c>
+      <c r="P114">
+        <v>5</v>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/indecnacional.xlsx
+++ b/data/indecnacional.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q114"/>
+  <dimension ref="A1:Q115"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="14" max="14" width="20.7109375" style="2" customWidth="1"/>
@@ -6663,6 +6663,61 @@
         </is>
       </c>
     </row>
+    <row r="115">
+      <c r="A115">
+        <v>1.9</v>
+      </c>
+      <c r="B115">
+        <v>1.3</v>
+      </c>
+      <c r="C115">
+        <v>2.1</v>
+      </c>
+      <c r="D115">
+        <v>0.4</v>
+      </c>
+      <c r="E115">
+        <v>3.3</v>
+      </c>
+      <c r="F115">
+        <v>1.5</v>
+      </c>
+      <c r="G115">
+        <v>2.9</v>
+      </c>
+      <c r="H115">
+        <v>1.6</v>
+      </c>
+      <c r="I115">
+        <v>0.9</v>
+      </c>
+      <c r="J115">
+        <v>4.2</v>
+      </c>
+      <c r="K115">
+        <v>1.7</v>
+      </c>
+      <c r="L115">
+        <v>1.6</v>
+      </c>
+      <c r="M115">
+        <v>1.8</v>
+      </c>
+      <c r="N115" s="2">
+        <v>46174</v>
+      </c>
+      <c r="O115">
+        <v>2026</v>
+      </c>
+      <c r="P115">
+        <v>6</v>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/indecnacional.xlsx
+++ b/data/indecnacional.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q115"/>
+  <dimension ref="A1:Q116"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="14" max="14" width="20.7109375" style="2" customWidth="1"/>
@@ -6718,6 +6718,61 @@
         </is>
       </c>
     </row>
+    <row r="116">
+      <c r="A116">
+        <v>2.1</v>
+      </c>
+      <c r="B116">
+        <v>2</v>
+      </c>
+      <c r="C116">
+        <v>1.5</v>
+      </c>
+      <c r="D116">
+        <v>-1.3</v>
+      </c>
+      <c r="E116">
+        <v>2.2</v>
+      </c>
+      <c r="F116">
+        <v>2.1</v>
+      </c>
+      <c r="G116">
+        <v>2.5</v>
+      </c>
+      <c r="H116">
+        <v>1.9</v>
+      </c>
+      <c r="I116">
+        <v>2.4</v>
+      </c>
+      <c r="J116">
+        <v>5</v>
+      </c>
+      <c r="K116">
+        <v>1.9</v>
+      </c>
+      <c r="L116">
+        <v>2.8</v>
+      </c>
+      <c r="M116">
+        <v>2.2</v>
+      </c>
+      <c r="N116" s="2">
+        <v>46204</v>
+      </c>
+      <c r="O116">
+        <v>2026</v>
+      </c>
+      <c r="P116">
+        <v>7</v>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
